--- a/Basics/Students.xlsx
+++ b/Basics/Students.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sambasivaraopendela/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sambasivaraopendela/Desktop/DataScience7AM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D66361C-E533-C64A-B645-F8ADB9A02487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65B604DB-A408-BF47-8032-A1EA9B7B40F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17060" xr2:uid="{B8A93BA6-7A10-B943-ACDB-77C2A4FE57B2}"/>
+    <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17060" xr2:uid="{7C3FDE5D-6562-5A4F-B579-DA1D5F8B74AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Marks</t>
+    <t>Maths</t>
+  </si>
+  <si>
+    <t>Science</t>
   </si>
   <si>
     <t>Std1</t>
@@ -54,6 +54,12 @@
   </si>
   <si>
     <t>Std3</t>
+  </si>
+  <si>
+    <t>Std4</t>
+  </si>
+  <si>
+    <t>Std5</t>
   </si>
 </sst>
 </file>
@@ -424,8 +430,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66C45A5C-DC3A-1A49-96E0-C95125BBFF71}">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED2B09BC-597A-6046-9850-4A9877081FEA}">
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -440,36 +446,58 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
+      <c r="B2">
+        <v>85</v>
+      </c>
       <c r="C2">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
+      <c r="B3">
+        <v>90</v>
+      </c>
       <c r="C3">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
+      <c r="B4">
+        <v>70</v>
+      </c>
       <c r="C4">
-        <v>78</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>60</v>
+      </c>
+      <c r="C5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>70</v>
+      </c>
+      <c r="C6">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
